--- a/script/templates/WeRootInterface_BS.xlsx
+++ b/script/templates/WeRootInterface_BS.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Obiettivo Performance Strategica UOC Servizio Ispettivo</t>
+          <t>Obiettivo Performance Strategica UOC Gestione Risorse Umane</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Obiettivo Performance Strategica UOC Investimenti e Energy Management</t>
+          <t>Obiettivo Performance Strategica UOC Gestione Risorse Tecniche</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/script/templates/WeRootInterface_BS.xlsx
+++ b/script/templates/WeRootInterface_BS.xlsx
@@ -450,7 +450,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BAA9003</t>
+          <t>2026_OB_PF_STG_BAA9003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -477,7 +477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSA9090</t>
+          <t>2026_OB_PF_STG_BSA9090</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OB_PF_STG_BSTA4800</t>
+          <t>2026_OB_PF_STG_BSTA4800</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9001</t>
+          <t>2026_OB_STG_BAA9001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9902</t>
+          <t>2026_OB_STG_BAA9902</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9903</t>
+          <t>2026_OB_STG_BAA9903</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9904</t>
+          <t>2026_OB_STG_BAA9904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9905</t>
+          <t>2026_OB_STG_BAA9905</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9906</t>
+          <t>2026_OB_STG_BAA9906</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9907</t>
+          <t>2026_OB_STG_BAA9907</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9908</t>
+          <t>2026_OB_STG_BAA9908</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9909</t>
+          <t>2026_OB_STG_BAA9909</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9910</t>
+          <t>2026_OB_STG_BAA9910</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9911</t>
+          <t>2026_OB_STG_BAA9911</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OB_STG_BAA9912</t>
+          <t>2026_OB_STG_BAA9912</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP0208</t>
+          <t>2026_OB_STG_BSCP0208</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -882,7 +882,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1404</t>
+          <t>2026_OB_STG_BSCP1404</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1407</t>
+          <t>2026_OB_STG_BSCP1407</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -936,7 +936,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1500</t>
+          <t>2026_OB_STG_BSCP1500</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1800</t>
+          <t>2026_OB_STG_BSCP1800</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP1810</t>
+          <t>2026_OB_STG_BSCP1810</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP2400</t>
+          <t>2026_OB_STG_BSCP2400</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OB_STG_BSCP3500</t>
+          <t>2026_OB_STG_BSCP3500</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1071,7 +1071,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0510</t>
+          <t>2026_OB_STG_BSCS0510</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0600</t>
+          <t>2026_OB_STG_BSCS0600</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0710</t>
+          <t>2026_OB_STG_BSCS0710</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1152,7 +1152,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS0903</t>
+          <t>2026_OB_STG_BSCS0903</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1010</t>
+          <t>2026_OB_STG_BSCS1010</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1402</t>
+          <t>2026_OB_STG_BSCS1402</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1403</t>
+          <t>2026_OB_STG_BSCS1403</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1404</t>
+          <t>2026_OB_STG_BSCS1404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1405</t>
+          <t>2026_OB_STG_BSCS1405</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1314,7 +1314,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS1600</t>
+          <t>2026_OB_STG_BSCS1600</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS2230</t>
+          <t>2026_OB_STG_BSCS2230</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OB_STG_BSCS3400</t>
+          <t>2026_OB_STG_BSCS3400</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA0120</t>
+          <t>2026_OB_STG_BSEA0120</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1422,7 +1422,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1000</t>
+          <t>2026_OB_STG_BSEA1000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA14081</t>
+          <t>2026_OB_STG_BSEA14081</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA1410</t>
+          <t>2026_OB_STG_BSEA1410</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2200</t>
+          <t>2026_OB_STG_BSEA2200</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2202</t>
+          <t>2026_OB_STG_BSEA2202</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2210</t>
+          <t>2026_OB_STG_BSEA2210</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2280</t>
+          <t>2026_OB_STG_BSEA2280</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2500</t>
+          <t>2026_OB_STG_BSEA2500</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2600</t>
+          <t>2026_OB_STG_BSEA2600</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1665,7 +1665,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA2810</t>
+          <t>2026_OB_STG_BSEA2810</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1692,7 +1692,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OB_STG_BSEA4820</t>
+          <t>2026_OB_STG_BSEA4820</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP0300</t>
+          <t>2026_OB_STG_BSMP0300</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1100</t>
+          <t>2026_OB_STG_BSMP1100</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1200</t>
+          <t>2026_OB_STG_BSMP1200</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1300</t>
+          <t>2026_OB_STG_BSMP1300</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1310</t>
+          <t>2026_OB_STG_BSMP1310</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1320</t>
+          <t>2026_OB_STG_BSMP1320</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP1401</t>
+          <t>2026_OB_STG_BSMP1401</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2000</t>
+          <t>2026_OB_STG_BSMP2000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP2610</t>
+          <t>2026_OB_STG_BSMP2610</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3000</t>
+          <t>2026_OB_STG_BSMP3000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1989,7 +1989,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3020</t>
+          <t>2026_OB_STG_BSMP3020</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2016,7 +2016,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OB_STG_BSMP3700</t>
+          <t>2026_OB_STG_BSMP3700</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1900</t>
+          <t>2026_OB_STG_BSOP1900</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1901</t>
+          <t>2026_OB_STG_BSOP1901</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP1911</t>
+          <t>2026_OB_STG_BSOP1911</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP2214</t>
+          <t>2026_OB_STG_BSOP2214</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3100</t>
+          <t>2026_OB_STG_BSOP3100</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2178,7 +2178,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3310</t>
+          <t>2026_OB_STG_BSOP3310</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2205,7 +2205,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3600</t>
+          <t>2026_OB_STG_BSOP3600</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP3800</t>
+          <t>2026_OB_STG_BSOP3800</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2259,7 +2259,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OB_STG_BSOP4000</t>
+          <t>2026_OB_STG_BSOP4000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2286,7 +2286,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1002</t>
+          <t>2026_OB_STG_BSTA1002</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA1003</t>
+          <t>2026_OB_STG_BSTA1003</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2340,7 +2340,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4010</t>
+          <t>2026_OB_STG_BSTA4010</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4100</t>
+          <t>2026_OB_STG_BSTA4100</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2394,7 +2394,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4110</t>
+          <t>2026_OB_STG_BSTA4110</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4111</t>
+          <t>2026_OB_STG_BSTA4111</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4330</t>
+          <t>2026_OB_STG_BSTA4330</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4600</t>
+          <t>2026_OB_STG_BSTA4600</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA4810</t>
+          <t>2026_OB_STG_BSTA4810</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2529,7 +2529,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OB_STG_BSTA5000</t>
+          <t>2026_OB_STG_BSTA5000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2556,7 +2556,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0811</t>
+          <t>2026_OB_STG_BSTR0811</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2583,7 +2583,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR0902</t>
+          <t>2026_OB_STG_BSTR0902</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2610,7 +2610,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2010</t>
+          <t>2026_OB_STG_BSTR2010</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OB_STG_BSTR2213</t>
+          <t>2026_OB_STG_BSTR2213</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2664,7 +2664,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1405</t>
+          <t>2026_OB_STG_BSU1405</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OB_STG_BSU1409</t>
+          <t>2026_OB_STG_BSU1409</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2718,7 +2718,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OB_STG_BSU4500</t>
+          <t>2026_OB_STG_BSU4500</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OB_STG_BSU4700</t>
+          <t>2026_OB_STG_BSU4700</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2772,7 +2772,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OB_STG_BSU7200</t>
+          <t>2026_OB_STG_BSU7200</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9095</t>
+          <t>2026_OB_STG_BSU9095</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2826,7 +2826,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9096</t>
+          <t>2026_OB_STG_BSU9096</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2853,7 +2853,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OB_STG_BSU9208</t>
+          <t>2026_OB_STG_BSU9208</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">

--- a/script/templates/WeRootInterface_BS.xlsx
+++ b/script/templates/WeRootInterface_BS.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2877,6 +2877,33 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026_OB_STG_BAA9913</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Obiettivo Performance Strategica UOC Investimenti e Energy Management</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BAA9913</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
